--- a/english_to_spanish_childrens_songbook_spreadsheet.xlsx
+++ b/english_to_spanish_childrens_songbook_spreadsheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ameli\Amelia\Church\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ameli\Amelia\Church\Sacred-Music-Translations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243AC769-B44D-4B81-A984-EBE62181B0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E878633F-D25C-4A07-B3E6-A8392B538C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{36536936-B9D7-4D2D-936B-383CE9944E54}"/>
   </bookViews>
@@ -1829,138 +1829,120 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D3">
-        <v>148</v>
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>219</v>
+        <v>277</v>
       </c>
       <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>221</v>
+        <v>39</v>
       </c>
       <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="B8">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D8">
-        <v>14</v>
+        <v>152</v>
+      </c>
+      <c r="E8" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>225</v>
+        <v>146</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="E10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>155</v>
       </c>
       <c r="B11">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
+        <v>240</v>
+      </c>
+      <c r="E11" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="E12" t="s">
         <v>456</v>
@@ -1968,262 +1950,280 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="E13" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="B14">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
+        <v>261</v>
+      </c>
+      <c r="E14" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>280</v>
       </c>
       <c r="E15" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="B16">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="E16" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+        <v>463</v>
+      </c>
+      <c r="G16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" t="s">
-        <v>7</v>
+        <v>205</v>
+      </c>
+      <c r="B17">
+        <v>289</v>
       </c>
       <c r="E17" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+        <v>463</v>
+      </c>
+      <c r="G17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18">
+        <v>290</v>
+      </c>
+      <c r="E18" t="s">
+        <v>463</v>
+      </c>
+      <c r="G18" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19">
+        <v>291</v>
+      </c>
+      <c r="E19" t="s">
+        <v>463</v>
+      </c>
+      <c r="G19" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E20" t="s">
+        <v>463</v>
+      </c>
+      <c r="G20" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E21" t="s">
+        <v>463</v>
+      </c>
+      <c r="G21" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22">
+        <v>293</v>
+      </c>
+      <c r="E22" t="s">
+        <v>463</v>
+      </c>
+      <c r="G22" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B23">
+        <v>294</v>
+      </c>
+      <c r="E23" t="s">
+        <v>463</v>
+      </c>
+      <c r="G23" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24">
+        <v>295</v>
+      </c>
+      <c r="E24" t="s">
+        <v>463</v>
+      </c>
+      <c r="G24" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25">
+        <v>296</v>
+      </c>
+      <c r="E25" t="s">
+        <v>463</v>
+      </c>
+      <c r="G25" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26">
+        <v>297</v>
+      </c>
+      <c r="E26" t="s">
+        <v>463</v>
+      </c>
+      <c r="G26" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27">
+        <v>298</v>
+      </c>
+      <c r="E27" t="s">
+        <v>463</v>
+      </c>
+      <c r="G27" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28">
+        <v>299</v>
+      </c>
+      <c r="E28" t="s">
+        <v>463</v>
+      </c>
+      <c r="G28" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B30">
         <v>8</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="E30" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B31">
         <v>10</v>
       </c>
-      <c r="E20" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="E31" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B32">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B24" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="E25" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D26" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B28">
-        <v>26</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D28">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A31" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A32" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D32">
-        <v>13</v>
+      <c r="E32" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B33">
-        <v>29</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D33">
-        <v>10</v>
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B34" t="s">
-        <v>21</v>
+        <v>231</v>
+      </c>
+      <c r="B34">
+        <v>19</v>
       </c>
       <c r="E34" t="s">
         <v>457</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
         <v>457</v>
@@ -2242,77 +2242,65 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B36">
-        <v>31</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D36">
-        <v>12</v>
+        <v>235</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B37">
-        <v>34</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D37">
-        <v>20</v>
+        <v>236</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B38">
-        <v>36</v>
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B39">
-        <v>37</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D39">
-        <v>24</v>
+        <v>238</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B40">
-        <v>38</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D40">
-        <v>22</v>
+        <v>239</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B41">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E41" t="s">
         <v>457</v>
@@ -2320,10 +2308,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E42" t="s">
         <v>457</v>
@@ -2331,63 +2319,54 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B44">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D44">
-        <v>25</v>
+        <v>245</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B45">
-        <v>42</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D45">
-        <v>26</v>
+        <v>246</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B46">
-        <v>44</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D46">
-        <v>28</v>
+        <v>249</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B47">
-        <v>46</v>
+        <v>250</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
       </c>
       <c r="E47" t="s">
         <v>457</v>
@@ -2395,10 +2374,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B48">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E48" t="s">
         <v>457</v>
@@ -2406,35 +2385,32 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B49">
-        <v>48</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D49">
-        <v>30</v>
+        <v>257</v>
+      </c>
+      <c r="B49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B50">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B51">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E51" t="s">
         <v>457</v>
@@ -2442,77 +2418,65 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B52">
-        <v>52</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D52">
-        <v>32</v>
+        <v>51</v>
+      </c>
+      <c r="E52" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B53">
-        <v>54</v>
+        <v>272</v>
+      </c>
+      <c r="B53" t="s">
+        <v>293</v>
       </c>
       <c r="E53" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B54">
-        <v>55</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D54">
-        <v>34</v>
+        <v>59</v>
+      </c>
+      <c r="E54" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B55">
-        <v>56</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D55">
-        <v>35</v>
+        <v>65</v>
+      </c>
+      <c r="E55" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B56">
-        <v>57</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D56">
-        <v>36</v>
+        <v>66</v>
+      </c>
+      <c r="E56" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B57" t="s">
-        <v>293</v>
+        <v>284</v>
+      </c>
+      <c r="B57">
+        <v>72</v>
       </c>
       <c r="E57" t="s">
         <v>457</v>
@@ -2520,24 +2484,21 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B58" t="s">
-        <v>294</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D58">
-        <v>37</v>
+        <v>295</v>
+      </c>
+      <c r="E58" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B59">
-        <v>59</v>
+        <v>286</v>
+      </c>
+      <c r="B59" t="s">
+        <v>296</v>
       </c>
       <c r="E59" t="s">
         <v>457</v>
@@ -2545,63 +2506,54 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B60">
-        <v>60</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D60">
-        <v>38</v>
+        <v>80</v>
+      </c>
+      <c r="E60" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>276</v>
+        <v>27</v>
       </c>
       <c r="B61">
-        <v>61</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D61">
-        <v>39</v>
+        <v>87</v>
+      </c>
+      <c r="E61" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>277</v>
+        <v>30</v>
       </c>
       <c r="B62">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>278</v>
+        <v>31</v>
       </c>
       <c r="B63">
-        <v>64</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D63">
-        <v>45</v>
+        <v>92</v>
+      </c>
+      <c r="E63" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>279</v>
+        <v>35</v>
       </c>
       <c r="B64">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="E64" t="s">
         <v>457</v>
@@ -2609,10 +2561,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="B65">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="E65" t="s">
         <v>457</v>
@@ -2620,46 +2572,43 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>281</v>
+        <v>41</v>
       </c>
       <c r="B66">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="E66" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>282</v>
+        <v>43</v>
       </c>
       <c r="B67">
-        <v>70</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D67">
-        <v>44</v>
+        <v>106</v>
+      </c>
+      <c r="E67" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>283</v>
+        <v>68</v>
       </c>
       <c r="B68">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="E68" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>284</v>
+        <v>72</v>
       </c>
       <c r="B69">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="E69" t="s">
         <v>457</v>
@@ -2667,10 +2616,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E70" t="s">
         <v>457</v>
@@ -2678,10 +2627,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B71" t="s">
-        <v>296</v>
+        <v>78</v>
+      </c>
+      <c r="B71">
+        <v>149</v>
       </c>
       <c r="E71" t="s">
         <v>457</v>
@@ -2689,63 +2638,54 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B72">
-        <v>74</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D72">
-        <v>42</v>
+        <v>79</v>
+      </c>
+      <c r="B72" t="s">
+        <v>307</v>
+      </c>
+      <c r="E72" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B73">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="B73" t="s">
+        <v>308</v>
       </c>
       <c r="E73" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="B74">
-        <v>77</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D74">
-        <v>48</v>
+        <v>154</v>
+      </c>
+      <c r="E74" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="B75">
-        <v>78</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D75">
-        <v>40</v>
+        <v>155</v>
+      </c>
+      <c r="E75" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>291</v>
+        <v>87</v>
       </c>
       <c r="B76">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
         <v>457</v>
@@ -2753,88 +2693,76 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>292</v>
+        <v>91</v>
       </c>
       <c r="B77">
-        <v>82</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D77">
-        <v>46</v>
+        <v>161</v>
+      </c>
+      <c r="E77" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B78" t="s">
-        <v>297</v>
+        <v>96</v>
+      </c>
+      <c r="B78">
+        <v>167</v>
       </c>
       <c r="E78" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B79" t="s">
-        <v>298</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D79">
-        <v>61</v>
+        <v>99</v>
+      </c>
+      <c r="B79">
+        <v>170</v>
+      </c>
+      <c r="E79" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="B80">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="E80" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="B81">
-        <v>88</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D81">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+      <c r="E81" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="B82">
-        <v>89</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D82">
-        <v>60</v>
+        <v>182</v>
+      </c>
+      <c r="E82" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="B83">
-        <v>90</v>
+        <v>194</v>
       </c>
       <c r="E83" t="s">
         <v>457</v>
@@ -2842,10 +2770,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B84">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="E84" t="s">
         <v>457</v>
@@ -2853,52 +2781,46 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B85">
-        <v>94</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D85">
-        <v>100</v>
+        <v>115</v>
+      </c>
+      <c r="B85" t="s">
+        <v>309</v>
+      </c>
+      <c r="E85" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="B86">
-        <v>95</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D86">
-        <v>99</v>
+        <v>199</v>
+      </c>
+      <c r="E86" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="B87">
-        <v>96</v>
+        <v>203</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D87">
-        <v>50</v>
+        <v>449</v>
+      </c>
+      <c r="E87" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B88">
-        <v>97</v>
+        <v>126</v>
+      </c>
+      <c r="B88" t="s">
+        <v>314</v>
       </c>
       <c r="E88" t="s">
         <v>457</v>
@@ -2906,74 +2828,65 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="B89">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="E89" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>37</v>
+        <v>133</v>
       </c>
       <c r="B90">
-        <v>99</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D90">
-        <v>52</v>
+        <v>215</v>
+      </c>
+      <c r="E90" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="B91">
-        <v>100</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D91">
-        <v>54</v>
+        <v>221</v>
+      </c>
+      <c r="E91" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="B92">
-        <v>102</v>
+        <v>222</v>
       </c>
       <c r="E92" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="B93">
-        <v>103</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D93">
-        <v>53</v>
+        <v>229</v>
+      </c>
+      <c r="E93" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="B94">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="E94" t="s">
         <v>457</v>
@@ -2981,2227 +2894,2314 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="B95">
-        <v>105</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D95">
-        <v>56</v>
+        <v>235</v>
+      </c>
+      <c r="E95" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="B96">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="E96" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="B97">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="E97" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>45</v>
+        <v>154</v>
       </c>
       <c r="B98">
-        <v>108</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D98">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+        <v>239</v>
+      </c>
+      <c r="E98" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B99">
-        <v>109</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D99">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+      <c r="B99" t="s">
+        <v>315</v>
+      </c>
+      <c r="E99" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="B100">
-        <v>110</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D100">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+        <v>247</v>
+      </c>
+      <c r="E100" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="B101">
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="E101" t="s">
-        <v>455</v>
-      </c>
-      <c r="G101" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B102">
-        <v>114</v>
+        <v>170</v>
+      </c>
+      <c r="B102" t="s">
+        <v>320</v>
       </c>
       <c r="E102" t="s">
-        <v>455</v>
-      </c>
-      <c r="G102" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="B103">
-        <v>116</v>
+        <v>256</v>
       </c>
       <c r="E103" t="s">
-        <v>455</v>
-      </c>
-      <c r="G103" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="B104">
-        <v>118</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D104">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+        <v>259</v>
+      </c>
+      <c r="E104" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="B105">
-        <v>119</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D105">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+        <v>262</v>
+      </c>
+      <c r="E105" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="B106">
-        <v>120</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D106">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+        <v>264</v>
+      </c>
+      <c r="E106" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B107" t="s">
-        <v>299</v>
+        <v>180</v>
+      </c>
+      <c r="B107">
+        <v>265</v>
       </c>
       <c r="E107" t="s">
-        <v>455</v>
-      </c>
-      <c r="G107" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="B108" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="E108" t="s">
-        <v>455</v>
-      </c>
-      <c r="G108" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="B109">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="E109" t="s">
-        <v>455</v>
-      </c>
-      <c r="G109" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="B110">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="E110" t="s">
-        <v>455</v>
-      </c>
-      <c r="G110" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
-        <v>58</v>
+        <v>186</v>
       </c>
       <c r="B111">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="E111" t="s">
-        <v>455</v>
-      </c>
-      <c r="G111" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B112" t="s">
-        <v>301</v>
+        <v>187</v>
+      </c>
+      <c r="B112">
+        <v>271</v>
       </c>
       <c r="E112" t="s">
-        <v>455</v>
-      </c>
-      <c r="G112" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B113" t="s">
-        <v>302</v>
+        <v>189</v>
+      </c>
+      <c r="B113">
+        <v>273</v>
       </c>
       <c r="E113" t="s">
-        <v>455</v>
-      </c>
-      <c r="G113" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B114">
-        <v>127</v>
+        <v>192</v>
+      </c>
+      <c r="B114" t="s">
+        <v>324</v>
       </c>
       <c r="E114" t="s">
-        <v>455</v>
-      </c>
-      <c r="G114" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B115" t="s">
-        <v>303</v>
+        <v>195</v>
+      </c>
+      <c r="B115">
+        <v>278</v>
       </c>
       <c r="E115" t="s">
-        <v>455</v>
-      </c>
-      <c r="G115" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B116" t="s">
-        <v>304</v>
+        <v>200</v>
+      </c>
+      <c r="B116">
+        <v>283</v>
       </c>
       <c r="E116" t="s">
-        <v>455</v>
-      </c>
-      <c r="G116" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B117">
-        <v>130</v>
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
+        <v>326</v>
       </c>
       <c r="E117" t="s">
-        <v>455</v>
-      </c>
-      <c r="G117" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B118">
-        <v>131</v>
+        <v>25</v>
+      </c>
+      <c r="B118" t="s">
+        <v>297</v>
       </c>
       <c r="E118" t="s">
-        <v>455</v>
-      </c>
-      <c r="G118" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="B119">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="E119" t="s">
         <v>455</v>
       </c>
-      <c r="G119" t="s">
-        <v>460</v>
-      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B120">
-        <v>134</v>
+        <v>258</v>
+      </c>
+      <c r="B120" t="s">
+        <v>24</v>
       </c>
       <c r="E120" t="s">
         <v>455</v>
       </c>
-      <c r="G120" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="2" t="s">
-        <v>68</v>
+        <v>265</v>
       </c>
       <c r="B121">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="E121" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
-        <v>69</v>
+        <v>268</v>
       </c>
       <c r="B122">
-        <v>136</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D122">
-        <v>74</v>
+        <v>54</v>
+      </c>
+      <c r="E122" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="2" t="s">
-        <v>70</v>
+        <v>283</v>
       </c>
       <c r="B123">
-        <v>138</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D123">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="E123" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
-        <v>71</v>
+        <v>288</v>
       </c>
       <c r="B124">
-        <v>140</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D124">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="E124" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B125">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E125" t="s">
-        <v>457</v>
+        <v>455</v>
+      </c>
+      <c r="G125" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B126">
-        <v>144</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D126">
-        <v>96</v>
+        <v>114</v>
+      </c>
+      <c r="E126" t="s">
+        <v>455</v>
+      </c>
+      <c r="G126" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B127" t="s">
-        <v>305</v>
+        <v>50</v>
+      </c>
+      <c r="B127">
+        <v>116</v>
       </c>
       <c r="E127" t="s">
-        <v>457</v>
+        <v>455</v>
+      </c>
+      <c r="G127" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B128" t="s">
-        <v>306</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D128">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+        <v>299</v>
+      </c>
+      <c r="E128" t="s">
+        <v>455</v>
+      </c>
+      <c r="G128" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B129">
-        <v>146</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D129">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+        <v>55</v>
+      </c>
+      <c r="B129" t="s">
+        <v>300</v>
+      </c>
+      <c r="E129" t="s">
+        <v>455</v>
+      </c>
+      <c r="G129" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B130">
-        <v>148</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D130">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+      <c r="E130" t="s">
+        <v>455</v>
+      </c>
+      <c r="G130" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="2" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B131">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E131" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G131" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B132" t="s">
-        <v>307</v>
+        <v>58</v>
+      </c>
+      <c r="B132">
+        <v>125</v>
       </c>
       <c r="E132" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G132" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B133" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E133" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G133" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B134">
-        <v>151</v>
+        <v>60</v>
+      </c>
+      <c r="B134" t="s">
+        <v>302</v>
       </c>
       <c r="E134" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G134" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B135">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E135" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G135" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B136">
-        <v>153</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="B136" t="s">
+        <v>303</v>
+      </c>
+      <c r="E136" t="s">
+        <v>455</v>
+      </c>
+      <c r="G136" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B137">
-        <v>154</v>
+        <v>63</v>
+      </c>
+      <c r="B137" t="s">
+        <v>304</v>
       </c>
       <c r="E137" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G137" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="B138">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E138" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G138" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B139">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="E139" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G139" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B140">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="E140" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+      <c r="G140" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B141">
-        <v>158</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D141">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+      <c r="E141" t="s">
+        <v>455</v>
+      </c>
+      <c r="G141" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B142">
-        <v>159</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D142">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+        <v>151</v>
+      </c>
+      <c r="E142" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="2" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B143">
-        <v>160</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D143">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+      <c r="E143" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="2" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="B144">
-        <v>161</v>
+        <v>216</v>
       </c>
       <c r="E144" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="B145">
-        <v>162</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D145">
-        <v>85</v>
+        <v>217</v>
+      </c>
+      <c r="E145" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="B146">
-        <v>163</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D146">
-        <v>84</v>
+        <v>219</v>
+      </c>
+      <c r="E146" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B147">
-        <v>164</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="D147">
-        <v>86</v>
+        <v>224</v>
+      </c>
+      <c r="E147" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="B148">
-        <v>166</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D148">
-        <v>88</v>
+        <v>225</v>
+      </c>
+      <c r="E148" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B149">
         <v>167</v>
       </c>
+      <c r="B149" t="s">
+        <v>317</v>
+      </c>
       <c r="E149" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B150">
-        <v>168</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D150">
-        <v>90</v>
+        <v>169</v>
+      </c>
+      <c r="B150" t="s">
+        <v>319</v>
+      </c>
+      <c r="E150" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="B151">
-        <v>169</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D151">
-        <v>91</v>
+        <v>255</v>
+      </c>
+      <c r="E151" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="B152">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="E152" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="B153">
-        <v>172</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D153">
-        <v>92</v>
+        <v>274</v>
+      </c>
+      <c r="E153" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="B154">
-        <v>174</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D154">
-        <v>94</v>
+        <v>279</v>
+      </c>
+      <c r="E154" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="B155">
-        <v>176</v>
+        <v>2</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="D155">
-        <v>75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="2" t="s">
-        <v>103</v>
+        <v>218</v>
       </c>
       <c r="B156">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>379</v>
+        <v>452</v>
       </c>
       <c r="D156">
-        <v>70</v>
+        <v>148</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="B157">
-        <v>178</v>
-      </c>
-      <c r="E157" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D157">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="B158">
-        <v>180</v>
-      </c>
-      <c r="E158" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
-        <v>106</v>
+        <v>223</v>
       </c>
       <c r="B159">
-        <v>182</v>
-      </c>
-      <c r="E159" t="s">
-        <v>457</v>
+        <v>9</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D159">
+        <v>14</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B160">
+        <v>12</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D160">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A161" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B161">
+        <v>16</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A162" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B162" t="s">
+        <v>8</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D162">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A163" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B163" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D163" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A164" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B164" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D164" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A165" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B165">
+        <v>26</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D165">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A166" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B166" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D166">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A167" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B167">
+        <v>29</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D167">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A168" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B168">
+        <v>31</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D168">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A169" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B169">
+        <v>34</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D169">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A170" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B170">
+        <v>37</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D170">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A171" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B171">
+        <v>38</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D171">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A172" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B172">
+        <v>41</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D172">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A173" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B173">
+        <v>42</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A174" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B174">
+        <v>44</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D174">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A175" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B175">
+        <v>48</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D175">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A176" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B176">
+        <v>52</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D176">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A177" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B177">
+        <v>55</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D177">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A178" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B178">
+        <v>56</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D178">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A179" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B179">
+        <v>57</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D179">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A180" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B180" t="s">
+        <v>294</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D180">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A181" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B181">
+        <v>60</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D181">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A182" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B182">
+        <v>61</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D182">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A183" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B183">
+        <v>64</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D183">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A184" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B184">
+        <v>70</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D184">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A185" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B185">
+        <v>74</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D185">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A186" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B186">
+        <v>77</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D186">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A187" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B187">
+        <v>78</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D187">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A188" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B188">
+        <v>82</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D188">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A189" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B189" t="s">
+        <v>298</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D189">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A190" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B190">
+        <v>88</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D190">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A191" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B191">
+        <v>89</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D191">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A192" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B192">
+        <v>94</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D192">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A193" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B193">
+        <v>95</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D193">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A194" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B194">
+        <v>96</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D194">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A195" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195">
+        <v>99</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D195">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A196" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B196">
+        <v>100</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D196">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A197" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B197">
+        <v>103</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D197">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A198" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B198">
+        <v>105</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D198">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A199" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B199">
+        <v>108</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D199">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A200" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B200">
+        <v>109</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D200">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A201" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B201">
+        <v>110</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D201">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A202" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B202">
+        <v>118</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D202">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A203" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B203">
+        <v>119</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D203">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A204" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B204">
+        <v>120</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D204">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A205" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B205">
+        <v>136</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D205">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A206" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B206">
+        <v>138</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D206">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A207" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B207">
+        <v>140</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D207">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A208" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B208">
+        <v>144</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D208">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A209" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B209" t="s">
+        <v>306</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D209">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A210" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B210">
+        <v>146</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D210">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A211" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B211">
+        <v>148</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D211">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A212" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B212">
+        <v>153</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A213" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B213">
+        <v>158</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D213">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A214" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B214">
+        <v>159</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D214">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A215" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B215">
+        <v>160</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D215">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A216" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B216">
+        <v>162</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D216">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A217" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B217">
+        <v>163</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D217">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A218" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B218">
+        <v>164</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D218">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A219" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B219">
+        <v>166</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D219">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A220" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B220">
+        <v>168</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D220">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A221" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B221">
+        <v>169</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D221">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A222" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B222">
+        <v>172</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D222">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A223" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B223">
+        <v>174</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D223">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A224" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B224">
+        <v>176</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D224">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A225" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B225">
+        <v>177</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D225">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A226" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B160">
+      <c r="B226">
         <v>188</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C226" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D160">
+      <c r="D226">
         <v>98</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A161" s="2" t="s">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A227" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B161">
+      <c r="B227">
         <v>189</v>
       </c>
-      <c r="C161" s="2" t="s">
+      <c r="C227" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="D161">
+      <c r="D227">
         <v>101</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A162" s="2" t="s">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A228" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B162">
+      <c r="B228">
         <v>190</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C228" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D162">
+      <c r="D228">
         <v>102</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A163" s="2" t="s">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A229" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B229">
+        <v>193</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D229">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A230" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B230">
+        <v>196</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D230">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A231" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B231" t="s">
+        <v>310</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D231">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A232" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B232" t="s">
+        <v>311</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D232">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A233" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B233" t="s">
+        <v>312</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D233" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A234" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B234">
+        <v>200</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D234">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A235" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B235">
+        <v>201</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D235">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A236" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B236">
+        <v>202</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D236">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A237" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B237">
+        <v>204</v>
+      </c>
+      <c r="G237" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A238" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B238" t="s">
+        <v>313</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D238" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A239" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B239">
+        <v>207</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D239">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A240" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B240">
+        <v>208</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D240">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A241" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B241">
+        <v>210</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D241">
         <v>110</v>
       </c>
-      <c r="B163">
-        <v>192</v>
-      </c>
-      <c r="E163" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A164" s="2" t="s">
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A242" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B242">
+        <v>211</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D242">
         <v>111</v>
       </c>
-      <c r="B164">
+    </row>
+    <row r="243" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A243" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B243">
+        <v>214</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D243">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A244" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B244">
+        <v>218</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D244">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A245" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B245">
+        <v>220</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D245">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A246" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B246">
+        <v>228</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D246">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A247" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B247">
+        <v>230</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D247">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A248" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B248">
+        <v>232</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D248">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A249" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B249">
+        <v>233</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D249">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A250" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B250">
+        <v>236</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D250">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A251" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B251" t="s">
+        <v>316</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D251">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A252" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B252">
+        <v>242</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D252">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A253" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B253">
+        <v>243</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D253">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A254" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B254">
+        <v>245</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D254">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A255" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B255">
+        <v>249</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D255">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A256" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B256">
+        <v>252</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D256">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A257" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B257" t="s">
+        <v>318</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D257" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A258" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B258">
+        <v>258</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D258">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A259" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B259">
+        <v>260</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D259">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A260" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B260">
+        <v>266</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D260">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A261" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B261" t="s">
+        <v>321</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D261">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A262" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B262">
+        <v>272</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D262">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A263" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B263" t="s">
+        <v>323</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D263" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A264" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D164">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A165" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B165">
+      <c r="B264">
+        <v>276</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D264">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A265" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E165" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A166" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B166">
-        <v>195</v>
-      </c>
-      <c r="E166" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A167" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B167">
-        <v>196</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D167">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A168" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B168" t="s">
-        <v>309</v>
-      </c>
-      <c r="E168" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A169" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B169" t="s">
-        <v>310</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D169">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A170" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B170" t="s">
-        <v>311</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D170">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A171" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B171" t="s">
-        <v>312</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D171" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A172" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B172">
+      <c r="B265">
+        <v>277</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D265">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A266" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B266">
+        <v>281</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D266">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A267" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E172" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A173" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B173">
-        <v>200</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D173">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A174" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B174">
+      <c r="B267">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A268" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D174">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A175" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B175">
-        <v>202</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D175">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A176" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B176">
+      <c r="B268" t="s">
+        <v>325</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D268">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A269" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E176" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A177" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B177">
-        <v>204</v>
-      </c>
-      <c r="G177" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A178" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B178" t="s">
-        <v>313</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D178" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A179" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B179" t="s">
-        <v>314</v>
-      </c>
-      <c r="E179" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A180" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B180">
-        <v>207</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D180">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A181" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B181">
-        <v>208</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D181">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A182" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B182">
-        <v>209</v>
-      </c>
-      <c r="E182" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A183" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B183">
-        <v>210</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D183">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A184" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B184">
-        <v>211</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D184">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A185" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B185">
-        <v>214</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D185">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A186" s="2" t="s">
+      <c r="B269">
+        <v>285</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D269">
         <v>133</v>
       </c>
-      <c r="B186">
-        <v>215</v>
-      </c>
-      <c r="E186" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A187" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B187">
-        <v>216</v>
-      </c>
-      <c r="E187" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A188" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B188">
-        <v>217</v>
-      </c>
-      <c r="E188" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A189" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B189">
-        <v>218</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D189">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A190" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B190">
-        <v>219</v>
-      </c>
-      <c r="E190" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A191" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B191">
-        <v>220</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D191">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A192" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B192">
-        <v>221</v>
-      </c>
-      <c r="E192" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A193" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B193">
-        <v>222</v>
-      </c>
-      <c r="E193" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A194" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B194">
-        <v>224</v>
-      </c>
-      <c r="E194" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A195" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B195">
-        <v>225</v>
-      </c>
-      <c r="E195" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A196" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B196">
-        <v>228</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D196">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A197" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B197">
-        <v>229</v>
-      </c>
-      <c r="E197" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A198" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B198">
-        <v>230</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D198">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A199" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B199">
-        <v>231</v>
-      </c>
-      <c r="E199" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A200" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B200">
-        <v>232</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D200">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A201" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B201">
-        <v>233</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D201">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A202" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B202">
-        <v>234</v>
-      </c>
-      <c r="E202" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A203" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B203">
-        <v>235</v>
-      </c>
-      <c r="E203" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A204" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B204">
-        <v>236</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D204">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A205" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B205">
-        <v>237</v>
-      </c>
-      <c r="E205" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A206" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B206">
-        <v>238</v>
-      </c>
-      <c r="E206" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A207" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B207">
-        <v>239</v>
-      </c>
-      <c r="E207" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A208" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B208">
-        <v>240</v>
-      </c>
-      <c r="E208" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A209" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B209" t="s">
-        <v>315</v>
-      </c>
-      <c r="E209" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A210" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B210" t="s">
-        <v>316</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D210">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A211" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B211">
-        <v>242</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D211">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A212" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B212">
-        <v>243</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D212">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A213" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B213">
-        <v>244</v>
-      </c>
-      <c r="E213" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A214" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B214">
-        <v>245</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D214">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A215" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B215">
-        <v>246</v>
-      </c>
-      <c r="E215" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A216" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B216">
-        <v>247</v>
-      </c>
-      <c r="E216" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A217" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B217">
-        <v>248</v>
-      </c>
-      <c r="E217" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A218" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B218">
-        <v>249</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D218">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A219" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B219">
-        <v>252</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D219">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A220" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B220" t="s">
-        <v>317</v>
-      </c>
-      <c r="E220" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A221" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B221" t="s">
-        <v>318</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D221" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A222" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B222" t="s">
-        <v>319</v>
-      </c>
-      <c r="E222" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A223" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B223" t="s">
-        <v>320</v>
-      </c>
-      <c r="E223" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A224" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B224">
-        <v>255</v>
-      </c>
-      <c r="E224" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A225" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B225">
-        <v>256</v>
-      </c>
-      <c r="E225" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A226" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B226">
-        <v>258</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D226">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A227" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B227">
-        <v>259</v>
-      </c>
-      <c r="E227" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A228" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B228">
-        <v>260</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D228">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A229" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B229">
-        <v>261</v>
-      </c>
-      <c r="E229" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A230" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B230">
-        <v>262</v>
-      </c>
-      <c r="E230" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A231" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B231">
-        <v>263</v>
-      </c>
-      <c r="E231" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A232" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B232">
-        <v>264</v>
-      </c>
-      <c r="E232" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A233" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B233">
-        <v>265</v>
-      </c>
-      <c r="E233" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A234" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B234">
-        <v>266</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D234">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A235" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B235" t="s">
-        <v>321</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D235">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A236" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B236" t="s">
-        <v>322</v>
-      </c>
-      <c r="E236" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A237" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B237">
-        <v>268</v>
-      </c>
-      <c r="E237" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A238" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B238">
-        <v>269</v>
-      </c>
-      <c r="E238" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A239" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B239">
-        <v>270</v>
-      </c>
-      <c r="E239" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A240" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B240">
-        <v>271</v>
-      </c>
-      <c r="E240" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A241" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B241">
-        <v>272</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D241">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A242" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B242">
-        <v>273</v>
-      </c>
-      <c r="E242" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A243" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B243">
-        <v>274</v>
-      </c>
-      <c r="E243" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A244" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B244" t="s">
-        <v>323</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D244" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A245" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B245" t="s">
-        <v>324</v>
-      </c>
-      <c r="E245" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A246" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B246">
-        <v>276</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D246">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A247" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B247">
-        <v>277</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D247">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A248" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B248">
-        <v>278</v>
-      </c>
-      <c r="E248" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A249" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B249">
-        <v>279</v>
-      </c>
-      <c r="E249" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A250" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B250">
-        <v>280</v>
-      </c>
-      <c r="E250" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A251" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B251">
-        <v>281</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D251">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A252" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B252">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A253" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B253">
-        <v>283</v>
-      </c>
-      <c r="E253" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A254" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B254" t="s">
-        <v>325</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D254">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A255" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B255" t="s">
-        <v>326</v>
-      </c>
-      <c r="E255" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A256" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B256">
-        <v>285</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="D256">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A257" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B257">
-        <v>288</v>
-      </c>
-      <c r="E257" t="s">
-        <v>463</v>
-      </c>
-      <c r="G257" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A258" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B258">
-        <v>289</v>
-      </c>
-      <c r="E258" t="s">
-        <v>463</v>
-      </c>
-      <c r="G258" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A259" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B259">
-        <v>290</v>
-      </c>
-      <c r="E259" t="s">
-        <v>463</v>
-      </c>
-      <c r="G259" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A260" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B260">
-        <v>291</v>
-      </c>
-      <c r="E260" t="s">
-        <v>463</v>
-      </c>
-      <c r="G260" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A261" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B261" t="s">
-        <v>327</v>
-      </c>
-      <c r="E261" t="s">
-        <v>463</v>
-      </c>
-      <c r="G261" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A262" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B262" t="s">
-        <v>328</v>
-      </c>
-      <c r="E262" t="s">
-        <v>463</v>
-      </c>
-      <c r="G262" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A263" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B263">
-        <v>293</v>
-      </c>
-      <c r="E263" t="s">
-        <v>463</v>
-      </c>
-      <c r="G263" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A264" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B264">
-        <v>294</v>
-      </c>
-      <c r="E264" t="s">
-        <v>463</v>
-      </c>
-      <c r="G264" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A265" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B265">
-        <v>295</v>
-      </c>
-      <c r="E265" t="s">
-        <v>463</v>
-      </c>
-      <c r="G265" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A266" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B266">
-        <v>296</v>
-      </c>
-      <c r="E266" t="s">
-        <v>463</v>
-      </c>
-      <c r="G266" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A267" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B267">
-        <v>297</v>
-      </c>
-      <c r="E267" t="s">
-        <v>463</v>
-      </c>
-      <c r="G267" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A268" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B268">
-        <v>298</v>
-      </c>
-      <c r="E268" t="s">
-        <v>463</v>
-      </c>
-      <c r="G268" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A269" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B269">
-        <v>299</v>
-      </c>
-      <c r="E269" t="s">
-        <v>463</v>
-      </c>
-      <c r="G269" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C270" s="2" t="s">
         <v>444</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C271" s="2" t="s">
         <v>447</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C272" s="2" t="s">
         <v>448</v>
       </c>
@@ -5237,6 +5237,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G273">
+    <sortCondition ref="E2:E273"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>